--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.9153</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2423</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.9562</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6331</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.9221</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6218</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9067</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.1267</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6873</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9131</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.1016</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6796</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8989</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.9492</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6308</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6514</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9394</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.9707</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6379</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9408</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.0188</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6535</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.0228</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6548</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9423</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.0104</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6508</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9415</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.0155</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6525</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.0218</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6545</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9422</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.0074</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6499</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9427</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.0121</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6514</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9406</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.0203</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.654</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.9359</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.2408</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6264</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.9344</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6259</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9514</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.934</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.6257</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.9383</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6272</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.9487</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6307</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.9418</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6283</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9062</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.9563</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6332</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.945</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6294</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9497</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.958</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.6337</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9617</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6251</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9651</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.9311</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6248</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9674</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.9382</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6271</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.9268</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6233</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9533</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.9517</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9252</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.9582</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6338</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9623</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.9385</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6272</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.9494</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6309</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9403</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.9735</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6388</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.9469</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.9537</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6323</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9554</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.9604</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6345</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.9395</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6276</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9348</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.921</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6214</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9807</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.9426</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.2328</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6286</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9514</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.9531</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6321</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9382</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.9715</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.6382</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.9627</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.6353</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9546</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.9623</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6352</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.9494</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2317</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.6309</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.9449</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.2433</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.6294</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9655</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.9384</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.6272</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9443</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.9917</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.6448</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9604</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.9833</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.642</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.9342</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.6258</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9345</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.9249</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.6227</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9177</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.9458</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.6297</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.9056</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.6162</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.8864</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6096</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9762999999999999</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.9844</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.2766</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.6424</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9661</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.9785</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.6405</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.9576</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.6336000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.0868</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.9116</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.0913</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.6764</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9136</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.0988</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.6787</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9622000000000001</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.0975</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.6783</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.9892</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.644</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.0023</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.6482</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9254</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.0162</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.6526999999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.9154</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2.0351</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.6588000000000001</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9569</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.9833</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.642</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.0007</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.6477000000000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9733000000000001</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2.0089</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.6503</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9746</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.974</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.639</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9631999999999999</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.9645</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.6359</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.9671</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.9744</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.6391</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.9726</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.6385999999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.0039</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.6487000000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9583</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.0168</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.6529</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.9725</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.6385</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9264</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.9725</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.6385</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.9031</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.1141</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.6834</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.1246</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.6866</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.1233</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.6862</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.1247</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.6866</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9477</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.9985</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.647</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9409</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.9991</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.6472</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.9814</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.6414</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9323</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.9751</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.6394</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9316</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.9823</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.6417</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.9504</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.6312</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.9459</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.6297</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.9503</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.6312</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.9563</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.6332</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.9625</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.6352</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9543</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.9626</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.6352</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9779</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.9503</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.6312</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9543</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.9626</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.6352</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.9221</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.6218</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.8741</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.1632</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.6983</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9408</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.9234</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.6222</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.9242</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.9246</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.6226</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.923</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.622</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.8928</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.6118</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.9156</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.6196</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9189000000000001</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.9161</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.6197</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.9295</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.2434</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.6242</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.8952</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.9285</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.6239</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.8874</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.9407</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9334</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.9106</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.6178</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9288999999999999</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.9154</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9745</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.9295</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.6242</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9508</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.9352</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.6262</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.9345</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.2773</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.6259</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9378</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.8911</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.6112</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9711</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.9325</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.6252</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9509</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.6269</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9411</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.9339</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.6257</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9369</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.8707</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.6042</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9224</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.9933</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.6453</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.9802</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.641</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8874</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.9407</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.628</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9509</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.6269</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8489</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.9613</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.6348</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.8489</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.9613</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.6348</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.8737</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.9081</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.617</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.9382</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.6272</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9308999999999999</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.9247</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6226</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9811</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.9195</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6209</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9789</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.9987</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.647</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>C18.1n7</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.637</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9831</v>
+        <v>0.9759</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9153</v>
+        <v>0.0262</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2423</v>
+        <v>0.271</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6486</v>
       </c>
     </row>
     <row r="3">
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9807</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9562</v>
+        <v>0.0473</v>
       </c>
       <c r="G3" t="n">
-        <v>0.277</v>
+        <v>0.2746</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6331</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8994</v>
+        <v>0.8583</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9221</v>
+        <v>0.102</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3634</v>
+        <v>0.3967</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6218</v>
+        <v>0.6229</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9067</v>
+        <v>0.9151</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1267</v>
+        <v>-0.1207</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3836</v>
+        <v>0.3849</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6873</v>
+        <v>0.6959</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9131</v>
+        <v>0.889</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1016</v>
+        <v>-0.1068</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3719</v>
+        <v>0.4064</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6796</v>
+        <v>0.6915</v>
       </c>
     </row>
     <row r="7">
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8989</v>
+        <v>0.9071</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9492</v>
+        <v>-0.0008</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3668</v>
+        <v>0.36</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6308</v>
+        <v>0.6576</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9389</v>
       </c>
       <c r="F8" t="n">
-        <v>2.012</v>
+        <v>-0.0026</v>
       </c>
       <c r="G8" t="n">
-        <v>0.347</v>
+        <v>0.3343</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6514</v>
+        <v>0.6581</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9394</v>
+        <v>0.9684</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9707</v>
+        <v>0.0503</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3595</v>
+        <v>0.3109</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6379</v>
+        <v>0.6405</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9408</v>
+        <v>0.9353</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0188</v>
+        <v>-0.0061</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3299</v>
+        <v>0.3352</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6535</v>
+        <v>0.6593</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9412</v>
+        <v>0.9305</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0228</v>
+        <v>-0.0174</v>
       </c>
       <c r="G11" t="n">
-        <v>0.332</v>
+        <v>0.353</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6548</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9423</v>
+        <v>0.9172</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0104</v>
+        <v>-0.0142</v>
       </c>
       <c r="G12" t="n">
-        <v>0.331</v>
+        <v>0.358</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6508</v>
+        <v>0.6619</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9415</v>
+        <v>0.9154</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0155</v>
+        <v>-0.0125</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3349</v>
+        <v>0.3586</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6525</v>
+        <v>0.6614</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9766</v>
+        <v>0.9301</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0218</v>
+        <v>-0.0181</v>
       </c>
       <c r="G14" t="n">
-        <v>0.256</v>
+        <v>0.3531</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6545</v>
+        <v>0.6632</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9422</v>
+        <v>0.9172</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0074</v>
+        <v>-0.0129</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3316</v>
+        <v>0.3579</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6499</v>
+        <v>0.6615</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9427</v>
+        <v>0.9165</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0121</v>
+        <v>-0.0118</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3326</v>
+        <v>0.3584</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6514</v>
+        <v>0.6612</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9406</v>
+        <v>0.9152</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0203</v>
+        <v>-0.0124</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3364</v>
+        <v>0.3584</v>
       </c>
       <c r="H17" t="n">
-        <v>0.654</v>
+        <v>0.6614</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9805</v>
+        <v>0.9695</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9359</v>
+        <v>0.0338</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2408</v>
+        <v>0.2833</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6264</v>
+        <v>0.6461</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9385</v>
+        <v>0.9657</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9344</v>
+        <v>0.063</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3418</v>
+        <v>0.285</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6259</v>
+        <v>0.6362</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9514</v>
+        <v>0.9649</v>
       </c>
       <c r="F20" t="n">
-        <v>1.934</v>
+        <v>0.0645</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3176</v>
+        <v>0.2855</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6257</v>
+        <v>0.6358</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.981</v>
+        <v>0.9644</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9383</v>
+        <v>0.0658</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2334</v>
+        <v>0.2859</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6272</v>
+        <v>0.6353</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9798</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9487</v>
+        <v>0.0545</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2338</v>
+        <v>0.3989</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6307</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9726</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9418</v>
+        <v>0.0582</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3489</v>
+        <v>0.2604</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6283</v>
+        <v>0.6379</v>
       </c>
     </row>
     <row r="24">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9062</v>
+        <v>0.9008</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9563</v>
+        <v>0.0604</v>
       </c>
       <c r="G24" t="n">
-        <v>0.379</v>
+        <v>0.3854</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6332</v>
+        <v>0.6371</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.979</v>
+        <v>0.9033</v>
       </c>
       <c r="F25" t="n">
-        <v>1.945</v>
+        <v>0.0524</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2338</v>
+        <v>0.3819</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6294</v>
+        <v>0.6398</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9497</v>
+        <v>0.9252</v>
       </c>
       <c r="F26" t="n">
-        <v>1.958</v>
+        <v>0.0192</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3416</v>
+        <v>0.3915</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6337</v>
+        <v>0.6509</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9617</v>
+        <v>0.9477</v>
       </c>
       <c r="F27" t="n">
-        <v>1.932</v>
+        <v>0.0499</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2817</v>
+        <v>0.3405</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6251</v>
+        <v>0.6407</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9651</v>
+        <v>0.9692</v>
       </c>
       <c r="F28" t="n">
-        <v>1.9311</v>
+        <v>0.0462</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2831</v>
+        <v>0.2832</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6248</v>
+        <v>0.6419</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9674</v>
+        <v>0.9685</v>
       </c>
       <c r="F29" t="n">
-        <v>1.9382</v>
+        <v>0.0496</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2873</v>
+        <v>0.2815</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6271</v>
+        <v>0.6408</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9264</v>
+        <v>0.9051</v>
       </c>
       <c r="F30" t="n">
-        <v>1.9268</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3544</v>
+        <v>0.396</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6233</v>
+        <v>0.6341</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9533</v>
+        <v>0.9646</v>
       </c>
       <c r="F31" t="n">
-        <v>1.9517</v>
+        <v>0.0623</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3031</v>
+        <v>0.2878</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9252</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9582</v>
+        <v>0.0456</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3522</v>
+        <v>0.3992</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6338</v>
+        <v>0.6421</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9623</v>
+        <v>0.9251</v>
       </c>
       <c r="F33" t="n">
-        <v>1.9385</v>
+        <v>0.0511</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2839</v>
+        <v>0.3538</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6272</v>
+        <v>0.6403</v>
       </c>
     </row>
     <row r="34">
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9519</v>
+        <v>0.9562</v>
       </c>
       <c r="F34" t="n">
-        <v>1.9494</v>
+        <v>0.062</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3651</v>
+        <v>0.364</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6309</v>
+        <v>0.6366000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9403</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>1.9735</v>
+        <v>0.0545</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3842</v>
+        <v>0.2337</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6388</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9469</v>
+        <v>0.977</v>
       </c>
       <c r="F36" t="n">
-        <v>1.9537</v>
+        <v>0.0439</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3516</v>
+        <v>0.2795</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6323</v>
+        <v>0.6427</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9554</v>
+        <v>0.9423</v>
       </c>
       <c r="F37" t="n">
-        <v>1.9604</v>
+        <v>0.0571</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3318</v>
+        <v>0.3562</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6345</v>
+        <v>0.6383</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9565</v>
+        <v>0.928</v>
       </c>
       <c r="F38" t="n">
-        <v>1.9395</v>
+        <v>0.0771</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3073</v>
+        <v>0.3667</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6276</v>
+        <v>0.6315</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9348</v>
+        <v>0.9374</v>
       </c>
       <c r="F39" t="n">
-        <v>1.921</v>
+        <v>0.1016</v>
       </c>
       <c r="G39" t="n">
         <v>0.3365</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6214</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9807</v>
+        <v>0.9668</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9426</v>
+        <v>0.0772</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2328</v>
+        <v>0.284</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6286</v>
+        <v>0.6314</v>
       </c>
     </row>
     <row r="41">
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9514</v>
+        <v>0.9569</v>
       </c>
       <c r="F41" t="n">
-        <v>1.9531</v>
+        <v>0.0576</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3655</v>
+        <v>0.3636</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6321</v>
+        <v>0.6381</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9382</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>1.9715</v>
+        <v>0.0538</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3842</v>
+        <v>0.2328</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6382</v>
+        <v>0.6394</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.945</v>
+        <v>0.977</v>
       </c>
       <c r="F43" t="n">
-        <v>1.9627</v>
+        <v>0.0462</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3534</v>
+        <v>0.2789</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6353</v>
+        <v>0.6419</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9546</v>
+        <v>0.9426</v>
       </c>
       <c r="F44" t="n">
-        <v>1.9623</v>
+        <v>0.0612</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3334</v>
+        <v>0.3532</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6352</v>
+        <v>0.6369</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9825</v>
+        <v>0.9594</v>
       </c>
       <c r="F45" t="n">
-        <v>1.9494</v>
+        <v>0.0825</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2317</v>
+        <v>0.2859</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6309</v>
+        <v>0.6296</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.978</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>1.9449</v>
+        <v>0.1019</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2433</v>
+        <v>0.2544</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6294</v>
+        <v>0.6229</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9655</v>
+        <v>0.9702</v>
       </c>
       <c r="F47" t="n">
-        <v>1.9384</v>
+        <v>0.0745</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2765</v>
+        <v>0.2805</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6272</v>
+        <v>0.6323</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9443</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>1.9917</v>
+        <v>0.0076</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3572</v>
+        <v>0.3753</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6448</v>
+        <v>0.6548</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9604</v>
+        <v>0.9857</v>
       </c>
       <c r="F49" t="n">
-        <v>1.9833</v>
+        <v>0.0525</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2999</v>
+        <v>0.2315</v>
       </c>
       <c r="H49" t="n">
-        <v>0.642</v>
+        <v>0.6398</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.952</v>
+        <v>0.9737</v>
       </c>
       <c r="F50" t="n">
-        <v>1.9342</v>
+        <v>0.018</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3121</v>
+        <v>0.2864</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6258</v>
+        <v>0.6513</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.9345</v>
+        <v>0.9524</v>
       </c>
       <c r="F51" t="n">
-        <v>1.9249</v>
+        <v>0.0488</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3213</v>
+        <v>0.2836</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6227</v>
+        <v>0.6411</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9177</v>
+        <v>0.9307</v>
       </c>
       <c r="F52" t="n">
-        <v>1.9458</v>
+        <v>0.0497</v>
       </c>
       <c r="G52" t="n">
-        <v>0.3401</v>
+        <v>0.3246</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6297</v>
+        <v>0.6408</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9727</v>
+        <v>0.9284</v>
       </c>
       <c r="F53" t="n">
-        <v>1.9056</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2623</v>
+        <v>0.356</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6162</v>
+        <v>0.6317</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9519</v>
+        <v>0.8951</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8864</v>
+        <v>0.0891</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2801</v>
+        <v>0.3942</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6096</v>
+        <v>0.6274</v>
       </c>
     </row>
     <row r="55">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9761</v>
       </c>
       <c r="F55" t="n">
-        <v>1.9844</v>
+        <v>0.0175</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2766</v>
+        <v>0.2829</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6424</v>
+        <v>0.6515</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9661</v>
+        <v>0.9869</v>
       </c>
       <c r="F56" t="n">
-        <v>1.9785</v>
+        <v>0.0114</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2992</v>
+        <v>0.2379</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6405</v>
+        <v>0.6535</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9755</v>
+        <v>0.9305</v>
       </c>
       <c r="F57" t="n">
-        <v>1.9576</v>
+        <v>-0.0171</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2617</v>
+        <v>0.3927</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6629</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.8872</v>
       </c>
       <c r="F58" t="n">
-        <v>2.0868</v>
+        <v>-0.1119</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3645</v>
+        <v>0.4067</v>
       </c>
       <c r="H58" t="n">
-        <v>0.675</v>
+        <v>0.6931</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9116</v>
+        <v>0.8438</v>
       </c>
       <c r="F59" t="n">
-        <v>2.0913</v>
+        <v>-0.1122</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3732</v>
+        <v>0.4473</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6764</v>
+        <v>0.6932</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9136</v>
+        <v>0.8834</v>
       </c>
       <c r="F60" t="n">
-        <v>2.0988</v>
+        <v>-0.1123</v>
       </c>
       <c r="G60" t="n">
-        <v>0.375</v>
+        <v>0.4166</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6787</v>
+        <v>0.6932</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>2.0975</v>
+        <v>-0.1138</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2905</v>
+        <v>0.4491</v>
       </c>
       <c r="H61" t="n">
-        <v>0.6783</v>
+        <v>0.6937</v>
       </c>
     </row>
     <row r="62">
@@ -2394,20 +2394,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9782</v>
+        <v>0.9739</v>
       </c>
       <c r="F62" t="n">
-        <v>1.9892</v>
+        <v>0.0068</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2579</v>
+        <v>0.2691</v>
       </c>
       <c r="H62" t="n">
-        <v>0.644</v>
+        <v>0.6551</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>2.0023</v>
+        <v>0.0011</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3548</v>
+        <v>0.2438</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6482</v>
+        <v>0.6569</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9254</v>
+        <v>0.9666</v>
       </c>
       <c r="F64" t="n">
-        <v>2.0162</v>
+        <v>-0.0308</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3613</v>
+        <v>0.2971</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6673</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.9154</v>
+        <v>0.9322</v>
       </c>
       <c r="F65" t="n">
-        <v>2.0351</v>
+        <v>-0.0468</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3866</v>
+        <v>0.3695</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6725</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9569</v>
+        <v>0.9356</v>
       </c>
       <c r="F66" t="n">
-        <v>1.9833</v>
+        <v>-0.0377</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3333</v>
+        <v>0.3839</v>
       </c>
       <c r="H66" t="n">
-        <v>0.642</v>
+        <v>0.6696</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9425</v>
+        <v>0.9326</v>
       </c>
       <c r="F67" t="n">
-        <v>2.0007</v>
+        <v>-0.0414</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3609</v>
+        <v>0.4053</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6708</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>2.0089</v>
+        <v>-0.0547</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2967</v>
+        <v>0.4097</v>
       </c>
       <c r="H68" t="n">
-        <v>0.6503</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9746</v>
+        <v>0.9342</v>
       </c>
       <c r="F69" t="n">
-        <v>1.974</v>
+        <v>0.0402</v>
       </c>
       <c r="G69" t="n">
-        <v>0.2494</v>
+        <v>0.3558</v>
       </c>
       <c r="H69" t="n">
-        <v>0.639</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9139</v>
       </c>
       <c r="F70" t="n">
-        <v>1.9645</v>
+        <v>0.062</v>
       </c>
       <c r="G70" t="n">
-        <v>0.2895</v>
+        <v>0.3798</v>
       </c>
       <c r="H70" t="n">
-        <v>0.6359</v>
+        <v>0.6366000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9671</v>
+        <v>0.9131</v>
       </c>
       <c r="F71" t="n">
-        <v>1.9744</v>
+        <v>0.0442</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2939</v>
+        <v>0.398</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6391</v>
+        <v>0.6425999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2718,16 +2718,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9202</v>
+        <v>0.9223</v>
       </c>
       <c r="F72" t="n">
-        <v>1.9726</v>
+        <v>0.045</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3771</v>
+        <v>0.3783</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.6423</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9749</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F73" t="n">
-        <v>2.0039</v>
+        <v>0.0017</v>
       </c>
       <c r="G73" t="n">
-        <v>0.289</v>
+        <v>0.2869</v>
       </c>
       <c r="H73" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6567</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9583</v>
+        <v>0.9475</v>
       </c>
       <c r="F74" t="n">
-        <v>2.0168</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.343</v>
+        <v>0.3641</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6529</v>
+        <v>0.6573</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9264</v>
+        <v>0.9319</v>
       </c>
       <c r="F75" t="n">
-        <v>1.9725</v>
+        <v>0.0127</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3273</v>
+        <v>0.3284</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6385</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9264</v>
+        <v>0.9319</v>
       </c>
       <c r="F76" t="n">
-        <v>1.9725</v>
+        <v>0.0127</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3273</v>
+        <v>0.3284</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6385</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="77">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9031</v>
+        <v>0.894</v>
       </c>
       <c r="F77" t="n">
-        <v>2.1141</v>
+        <v>-0.1263</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3823</v>
+        <v>0.3926</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6834</v>
+        <v>0.6976</v>
       </c>
     </row>
     <row r="78">
@@ -2910,16 +2910,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9064</v>
+        <v>0.8996</v>
       </c>
       <c r="F78" t="n">
-        <v>2.1246</v>
+        <v>-0.1354</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3811</v>
+        <v>0.3936</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6866</v>
+        <v>0.7004</v>
       </c>
     </row>
     <row r="79">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9065</v>
+        <v>0.8986</v>
       </c>
       <c r="F79" t="n">
-        <v>2.1233</v>
+        <v>-0.1426</v>
       </c>
       <c r="G79" t="n">
-        <v>0.382</v>
+        <v>0.3936</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6862</v>
+        <v>0.7026</v>
       </c>
     </row>
     <row r="80">
@@ -2974,16 +2974,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9065</v>
+        <v>0.8998</v>
       </c>
       <c r="F80" t="n">
-        <v>2.1247</v>
+        <v>-0.136</v>
       </c>
       <c r="G80" t="n">
-        <v>0.3811</v>
+        <v>0.3936</v>
       </c>
       <c r="H80" t="n">
-        <v>0.6866</v>
+        <v>0.7006</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9477</v>
+        <v>0.9584</v>
       </c>
       <c r="F81" t="n">
-        <v>1.9985</v>
+        <v>0.0194</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3256</v>
+        <v>0.3138</v>
       </c>
       <c r="H81" t="n">
-        <v>0.647</v>
+        <v>0.6509</v>
       </c>
     </row>
     <row r="82">
@@ -3034,20 +3034,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9409</v>
+        <v>0.9253</v>
       </c>
       <c r="F82" t="n">
-        <v>1.9991</v>
+        <v>0.0203</v>
       </c>
       <c r="G82" t="n">
-        <v>0.3607</v>
+        <v>0.3671</v>
       </c>
       <c r="H82" t="n">
-        <v>0.6472</v>
+        <v>0.6506</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.8815</v>
+        <v>0.9692</v>
       </c>
       <c r="F83" t="n">
-        <v>1.9814</v>
+        <v>0.0074</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4072</v>
+        <v>0.2497</v>
       </c>
       <c r="H83" t="n">
-        <v>0.6414</v>
+        <v>0.6549</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9323</v>
+        <v>0.973</v>
       </c>
       <c r="F84" t="n">
-        <v>1.9751</v>
+        <v>0.0038</v>
       </c>
       <c r="G84" t="n">
-        <v>0.3365</v>
+        <v>0.2437</v>
       </c>
       <c r="H84" t="n">
-        <v>0.6394</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9316</v>
+        <v>0.9696</v>
       </c>
       <c r="F85" t="n">
-        <v>1.9823</v>
+        <v>0.0062</v>
       </c>
       <c r="G85" t="n">
-        <v>0.3381</v>
+        <v>0.2481</v>
       </c>
       <c r="H85" t="n">
-        <v>0.6417</v>
+        <v>0.6553</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9565</v>
+        <v>0.9695</v>
       </c>
       <c r="F86" t="n">
-        <v>1.9504</v>
+        <v>0.031</v>
       </c>
       <c r="G86" t="n">
-        <v>0.3108</v>
+        <v>0.2802</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6312</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9805</v>
+        <v>0.9206</v>
       </c>
       <c r="F87" t="n">
-        <v>1.9459</v>
+        <v>0.035</v>
       </c>
       <c r="G87" t="n">
-        <v>0.2459</v>
+        <v>0.3924</v>
       </c>
       <c r="H87" t="n">
-        <v>0.6297</v>
+        <v>0.6457000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9779</v>
+        <v>0.9497</v>
       </c>
       <c r="F88" t="n">
-        <v>1.9503</v>
+        <v>0.0173</v>
       </c>
       <c r="G88" t="n">
-        <v>0.2484</v>
+        <v>0.3412</v>
       </c>
       <c r="H88" t="n">
-        <v>0.6312</v>
+        <v>0.6516</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.969</v>
+        <v>0.9298</v>
       </c>
       <c r="F89" t="n">
-        <v>1.9563</v>
+        <v>0.0439</v>
       </c>
       <c r="G89" t="n">
-        <v>0.2833</v>
+        <v>0.3614</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6332</v>
+        <v>0.6427</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.945</v>
+        <v>0.977</v>
       </c>
       <c r="F90" t="n">
-        <v>1.9625</v>
+        <v>0.0464</v>
       </c>
       <c r="G90" t="n">
-        <v>0.3534</v>
+        <v>0.2787</v>
       </c>
       <c r="H90" t="n">
-        <v>0.6352</v>
+        <v>0.6419</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9543</v>
+        <v>0.9427</v>
       </c>
       <c r="F91" t="n">
-        <v>1.9626</v>
+        <v>0.0611</v>
       </c>
       <c r="G91" t="n">
-        <v>0.3335</v>
+        <v>0.3532</v>
       </c>
       <c r="H91" t="n">
-        <v>0.6352</v>
+        <v>0.6369</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9779</v>
+        <v>0.9497</v>
       </c>
       <c r="F92" t="n">
-        <v>1.9503</v>
+        <v>0.0173</v>
       </c>
       <c r="G92" t="n">
-        <v>0.2484</v>
+        <v>0.3412</v>
       </c>
       <c r="H92" t="n">
-        <v>0.6312</v>
+        <v>0.6516</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9543</v>
+        <v>0.9427</v>
       </c>
       <c r="F93" t="n">
-        <v>1.9626</v>
+        <v>0.0611</v>
       </c>
       <c r="G93" t="n">
-        <v>0.3335</v>
+        <v>0.3532</v>
       </c>
       <c r="H93" t="n">
-        <v>0.6352</v>
+        <v>0.6369</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.8994</v>
+        <v>0.8583</v>
       </c>
       <c r="F94" t="n">
-        <v>1.9221</v>
+        <v>0.102</v>
       </c>
       <c r="G94" t="n">
-        <v>0.3634</v>
+        <v>0.3967</v>
       </c>
       <c r="H94" t="n">
-        <v>0.6218</v>
+        <v>0.6229</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8741</v>
+        <v>0.7796</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1632</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="G95" t="n">
-        <v>0.398</v>
+        <v>0.4701</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6983</v>
+        <v>0.6873</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9408</v>
+        <v>0.8593</v>
       </c>
       <c r="F96" t="n">
-        <v>1.9234</v>
+        <v>0.097</v>
       </c>
       <c r="G96" t="n">
-        <v>0.2999</v>
+        <v>0.3951</v>
       </c>
       <c r="H96" t="n">
-        <v>0.6222</v>
+        <v>0.6246</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9414</v>
+        <v>0.8395</v>
       </c>
       <c r="F97" t="n">
-        <v>1.9242</v>
+        <v>0.0984</v>
       </c>
       <c r="G97" t="n">
-        <v>0.298</v>
+        <v>0.4137</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6241</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9439</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="F98" t="n">
-        <v>1.9246</v>
+        <v>0.0892</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3089</v>
+        <v>0.3095</v>
       </c>
       <c r="H98" t="n">
-        <v>0.6226</v>
+        <v>0.6273</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.931</v>
+        <v>0.9321</v>
       </c>
       <c r="F99" t="n">
-        <v>1.923</v>
+        <v>0.089</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3175</v>
+        <v>0.3201</v>
       </c>
       <c r="H99" t="n">
-        <v>0.622</v>
+        <v>0.6274</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.8862</v>
       </c>
       <c r="F100" t="n">
-        <v>1.8928</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="G100" t="n">
-        <v>0.3065</v>
+        <v>0.3795</v>
       </c>
       <c r="H100" t="n">
-        <v>0.6118</v>
+        <v>0.6286</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9643</v>
+        <v>0.8681</v>
       </c>
       <c r="F101" t="n">
-        <v>1.9156</v>
+        <v>0.0747</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2521</v>
+        <v>0.3962</v>
       </c>
       <c r="H101" t="n">
-        <v>0.6196</v>
+        <v>0.6323</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.8832</v>
       </c>
       <c r="F102" t="n">
-        <v>1.9161</v>
+        <v>0.0649</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3281</v>
+        <v>0.3802</v>
       </c>
       <c r="H102" t="n">
-        <v>0.6197</v>
+        <v>0.6356000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.971</v>
+        <v>0.92</v>
       </c>
       <c r="F103" t="n">
-        <v>1.9295</v>
+        <v>0.0987</v>
       </c>
       <c r="G103" t="n">
-        <v>0.2434</v>
+        <v>0.3507</v>
       </c>
       <c r="H103" t="n">
-        <v>0.6242</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.8952</v>
+        <v>0.9331</v>
       </c>
       <c r="F104" t="n">
-        <v>1.9285</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G104" t="n">
-        <v>0.383</v>
+        <v>0.3113</v>
       </c>
       <c r="H104" t="n">
-        <v>0.6239</v>
+        <v>0.6279</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.8874</v>
+        <v>0.9527</v>
       </c>
       <c r="F105" t="n">
-        <v>1.9407</v>
+        <v>0.0733</v>
       </c>
       <c r="G105" t="n">
-        <v>0.386</v>
+        <v>0.2761</v>
       </c>
       <c r="H105" t="n">
-        <v>0.628</v>
+        <v>0.6327</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9334</v>
+        <v>0.9402</v>
       </c>
       <c r="F106" t="n">
-        <v>1.9106</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3124</v>
+        <v>0.2982</v>
       </c>
       <c r="H106" t="n">
-        <v>0.6178</v>
+        <v>0.6254999999999999</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.8839</v>
       </c>
       <c r="F107" t="n">
-        <v>1.9154</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="G107" t="n">
-        <v>0.3167</v>
+        <v>0.3812</v>
       </c>
       <c r="H107" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6334</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9745</v>
+        <v>0.9385</v>
       </c>
       <c r="F108" t="n">
-        <v>1.9295</v>
+        <v>0.113</v>
       </c>
       <c r="G108" t="n">
-        <v>0.2412</v>
+        <v>0.3321</v>
       </c>
       <c r="H108" t="n">
-        <v>0.6242</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9508</v>
+        <v>0.9465</v>
       </c>
       <c r="F109" t="n">
-        <v>1.9352</v>
+        <v>0.0988</v>
       </c>
       <c r="G109" t="n">
-        <v>0.3104</v>
+        <v>0.3318</v>
       </c>
       <c r="H109" t="n">
-        <v>0.6262</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.963</v>
+        <v>0.9023</v>
       </c>
       <c r="F110" t="n">
-        <v>1.9345</v>
+        <v>0.0977</v>
       </c>
       <c r="G110" t="n">
-        <v>0.2773</v>
+        <v>0.3852</v>
       </c>
       <c r="H110" t="n">
-        <v>0.6259</v>
+        <v>0.6244</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9378</v>
+        <v>0.8905</v>
       </c>
       <c r="F111" t="n">
-        <v>1.8911</v>
+        <v>0.1152</v>
       </c>
       <c r="G111" t="n">
-        <v>0.3115</v>
+        <v>0.3855</v>
       </c>
       <c r="H111" t="n">
-        <v>0.6112</v>
+        <v>0.6183</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9711</v>
+        <v>0.9369</v>
       </c>
       <c r="F112" t="n">
-        <v>1.9325</v>
+        <v>0.1201</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2484</v>
+        <v>0.3336</v>
       </c>
       <c r="H112" t="n">
-        <v>0.6252</v>
+        <v>0.6166</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9509</v>
+        <v>0.9453</v>
       </c>
       <c r="F113" t="n">
-        <v>1.9375</v>
+        <v>0.1052</v>
       </c>
       <c r="G113" t="n">
-        <v>0.3103</v>
+        <v>0.3332</v>
       </c>
       <c r="H113" t="n">
-        <v>0.6269</v>
+        <v>0.6218</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9411</v>
+        <v>0.9025</v>
       </c>
       <c r="F114" t="n">
-        <v>1.9339</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>0.3273</v>
+        <v>0.3853</v>
       </c>
       <c r="H114" t="n">
-        <v>0.6257</v>
+        <v>0.6254</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9369</v>
+        <v>0.9346</v>
       </c>
       <c r="F115" t="n">
-        <v>1.8707</v>
+        <v>0.1195</v>
       </c>
       <c r="G115" t="n">
-        <v>0.3044</v>
+        <v>0.3083</v>
       </c>
       <c r="H115" t="n">
-        <v>0.6042</v>
+        <v>0.6168</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9224</v>
+        <v>0.8646</v>
       </c>
       <c r="F116" t="n">
-        <v>1.9933</v>
+        <v>-0.0119</v>
       </c>
       <c r="G116" t="n">
-        <v>0.3551</v>
+        <v>0.4228</v>
       </c>
       <c r="H116" t="n">
-        <v>0.6453</v>
+        <v>0.6612</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.916</v>
+        <v>0.8624000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>1.9802</v>
+        <v>-0.0106</v>
       </c>
       <c r="G117" t="n">
-        <v>0.3641</v>
+        <v>0.4262</v>
       </c>
       <c r="H117" t="n">
-        <v>0.641</v>
+        <v>0.6608000000000001</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.8874</v>
+        <v>0.9527</v>
       </c>
       <c r="F118" t="n">
-        <v>1.9407</v>
+        <v>0.0733</v>
       </c>
       <c r="G118" t="n">
-        <v>0.386</v>
+        <v>0.2761</v>
       </c>
       <c r="H118" t="n">
-        <v>0.628</v>
+        <v>0.6327</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9509</v>
+        <v>0.9453</v>
       </c>
       <c r="F119" t="n">
-        <v>1.9375</v>
+        <v>0.1052</v>
       </c>
       <c r="G119" t="n">
-        <v>0.3103</v>
+        <v>0.3332</v>
       </c>
       <c r="H119" t="n">
-        <v>0.6269</v>
+        <v>0.6218</v>
       </c>
     </row>
     <row r="120">
@@ -4254,16 +4254,16 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8489</v>
+        <v>0.8351</v>
       </c>
       <c r="F120" t="n">
-        <v>1.9613</v>
+        <v>0.0383</v>
       </c>
       <c r="G120" t="n">
-        <v>0.4061</v>
+        <v>0.416</v>
       </c>
       <c r="H120" t="n">
-        <v>0.6348</v>
+        <v>0.6446</v>
       </c>
     </row>
     <row r="121">
@@ -4286,16 +4286,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8489</v>
+        <v>0.8351</v>
       </c>
       <c r="F121" t="n">
-        <v>1.9613</v>
+        <v>0.0383</v>
       </c>
       <c r="G121" t="n">
-        <v>0.4061</v>
+        <v>0.416</v>
       </c>
       <c r="H121" t="n">
-        <v>0.6348</v>
+        <v>0.6446</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.8737</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>1.9081</v>
+        <v>0.1042</v>
       </c>
       <c r="G122" t="n">
-        <v>0.3885</v>
+        <v>0.3434</v>
       </c>
       <c r="H122" t="n">
-        <v>0.617</v>
+        <v>0.6221</v>
       </c>
     </row>
     <row r="123">
@@ -4350,16 +4350,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9455</v>
       </c>
       <c r="F123" t="n">
-        <v>1.9382</v>
+        <v>0.1052</v>
       </c>
       <c r="G123" t="n">
-        <v>0.3277</v>
+        <v>0.3334</v>
       </c>
       <c r="H123" t="n">
-        <v>0.6272</v>
+        <v>0.6217</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>1.9247</v>
+        <v>0.1127</v>
       </c>
       <c r="G124" t="n">
-        <v>0.3321</v>
+        <v>0.3642</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6226</v>
+        <v>0.6192</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9811</v>
+        <v>0.9596</v>
       </c>
       <c r="F125" t="n">
-        <v>1.9195</v>
+        <v>0.0451</v>
       </c>
       <c r="G125" t="n">
-        <v>0.2403</v>
+        <v>0.3308</v>
       </c>
       <c r="H125" t="n">
-        <v>0.6209</v>
+        <v>0.6423</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9789</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>1.9987</v>
+        <v>0.025</v>
       </c>
       <c r="G126" t="n">
-        <v>0.2651</v>
+        <v>0.2933</v>
       </c>
       <c r="H126" t="n">
-        <v>0.647</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9567</v>
+        <v>0.9429</v>
       </c>
       <c r="F127" t="n">
-        <v>1.968</v>
+        <v>0.0436</v>
       </c>
       <c r="G127" t="n">
-        <v>0.3018</v>
+        <v>0.3702</v>
       </c>
       <c r="H127" t="n">
-        <v>0.637</v>
+        <v>0.6428</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/C18.1n7/RANDOMSEARCH_DETAILS_C18.1n7.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -612,7 +612,7 @@
         <v>-0.1068</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4064</v>
+        <v>0.4062</v>
       </c>
       <c r="H6" t="n">
         <v>0.6915</v>
